--- a/data/simulations/xa_fixed_v1/SIM_XA_FIXED_seed_20260809/competition_xlsx/SIM_XA_FIXED比赛规则.xlsx
+++ b/data/simulations/xa_fixed_v1/SIM_XA_FIXED_seed_20260809/competition_xlsx/SIM_XA_FIXED比赛规则.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H49"/>
+  <dimension ref="A1:H52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -1300,83 +1300,119 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>所有内容均为随机模拟规则，不是历史比赛正式规则。</t>
+          <t>这是模拟执行规则包；XA 参数来源和候选结算服务必须按 provenance 分别解释。</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>第一年无订单</t>
+          <t>规则模式</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>fixed_XA_rules_random_orders</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>破产标准</t>
+          <t>参数来源</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>["cash_flow_break", "negative_equity"]</t>
+          <t>observed_formal_XA</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>评分公式</t>
+          <t>场景覆盖</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>score = owner_equity * (1 + development_potential / 100)</t>
+          <t>{}</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>九.重要参数</t>
+          <t>正式 XA 参数记录第一年无订单</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
+          <t>破产标准</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>["cash_flow_break", "negative_equity"]</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>评分公式</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>score = owner_equity * (1 + development_potential / 100)</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>九.重要参数</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
           <t>违约金比例</t>
         </is>
       </c>
-      <c r="B49" t="n">
+      <c r="B52" t="n">
         <v>0.2</v>
       </c>
-      <c r="C49" t="inlineStr">
+      <c r="C52" t="inlineStr">
         <is>
           <t>初始现金</t>
         </is>
       </c>
-      <c r="D49" t="inlineStr">
+      <c r="D52" t="inlineStr">
         <is>
           <t>675W</t>
         </is>
       </c>
-      <c r="E49" t="inlineStr">
+      <c r="E52" t="inlineStr">
         <is>
           <t>管理费</t>
         </is>
       </c>
-      <c r="F49" t="inlineStr">
+      <c r="F52" t="inlineStr">
         <is>
           <t>14W</t>
         </is>
       </c>
-      <c r="G49" t="inlineStr">
+      <c r="G52" t="inlineStr">
         <is>
           <t>所得税率</t>
         </is>
       </c>
-      <c r="H49" t="n">
+      <c r="H52" t="n">
         <v>0.25</v>
       </c>
     </row>
